--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>id</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>林奈同学将提升礼物的各项数值</t>
+  </si>
+  <si>
+    <t>测试</t>
+  </si>
+  <si>
+    <t>占坑测试用</t>
   </si>
 </sst>
 </file>
@@ -1043,6 +1049,12 @@
       <c r="A5">
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="11430"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,10 +34,10 @@
     <t>id</t>
   </si>
   <si>
-    <t>名称</t>
+    <t>text</t>
   </si>
   <si>
-    <t>描述</t>
+    <t>description</t>
   </si>
   <si>
     <t>制造</t>

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="11430"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +62,12 @@
   </si>
   <si>
     <t>占坑测试用</t>
+  </si>
+  <si>
+    <t>取出物品</t>
+  </si>
+  <si>
+    <t>将袋子中的物品放置到桌上</t>
   </si>
 </sst>
 </file>
@@ -1060,6 +1066,12 @@
       <c r="A6">
         <v>5</v>
       </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>id</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t>将袋子中的物品放置到桌上</t>
+  </si>
+  <si>
+    <t>提交顺序</t>
+  </si>
+  <si>
+    <t>若物品具有多种功能，则会按制造，拆卸，美化的顺序进行</t>
   </si>
 </sst>
 </file>
@@ -1001,8 +1007,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="25" style="1" customWidth="1"/>
   </cols>
@@ -1071,6 +1077,17 @@
       </c>
       <c r="C6" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="7" ht="42" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -73,7 +73,7 @@
     <t>提交顺序</t>
   </si>
   <si>
-    <t>若物品具有多种功能，则会按制造，拆卸，美化的顺序进行</t>
+    <t>若物品具有多种功能，则会按拆卸，制造，美化的顺序进行</t>
   </si>
 </sst>
 </file>

--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -64,16 +64,16 @@
     <t>占坑测试用</t>
   </si>
   <si>
-    <t>取出物品</t>
-  </si>
-  <si>
-    <t>将袋子中的物品放置到桌上</t>
-  </si>
-  <si>
-    <t>提交顺序</t>
-  </si>
-  <si>
-    <t>若物品具有多种功能，则会按拆卸，制造，美化的顺序进行</t>
+    <t>取出</t>
+  </si>
+  <si>
+    <t>将书包中的物品放置到桌上</t>
+  </si>
+  <si>
+    <t>顺序</t>
+  </si>
+  <si>
+    <t>具有多种功能按拆卸，制造，美化的顺序进行</t>
   </si>
 </sst>
 </file>
@@ -1007,8 +1007,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="25" style="1" customWidth="1"/>
   </cols>
@@ -1079,7 +1079,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="42" spans="1:3">
+    <row r="7" ht="28" spans="1:3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1088,6 +1088,11 @@
       </c>
       <c r="C7" s="1" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
